--- a/data/trans_orig/AIRE_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70811</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89367</t>
+          <t>88755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37249</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55805</t>
+          <t>56083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>40672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65263</t>
+          <t>65350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79413</t>
+          <t>79119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>18075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52267</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90879</t>
+          <t>91000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111043</t>
+          <t>111003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61508</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83244</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157716</t>
+          <t>158244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191387</t>
+          <t>192435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>22695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44386</t>
+          <t>44412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34669</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>36248</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>64282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>90906</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107353</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34059</t>
+          <t>33775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>48530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61515</t>
+          <t>60707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>236389</t>
+          <t>236932</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>272541</t>
+          <t>269341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260634</t>
+          <t>259784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294445</t>
+          <t>293464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>504212</t>
+          <t>506638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>556195</t>
+          <t>555525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91897</t>
+          <t>91354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85461</t>
+          <t>86442</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119272</t>
+          <t>120122</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>151997</t>
+          <t>152667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>203980</t>
+          <t>201554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46135</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38899</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52277</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>31097</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25168</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36533</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56082</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70533</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88755</t>
+          <t>86098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22448</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16306</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29684</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22991</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17555</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28920</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>42,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46233</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37861</t>
+          <t>37174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>54946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34514</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28114</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39104</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36702</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31591</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40946</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>75,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>37006</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30614</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72670</t>
+          <t>71520</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65350</t>
+          <t>63732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79119</t>
+          <t>78315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12550</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7960</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18950</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11736</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7492</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16847</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24524</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18075</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24157</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19408</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14776</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46818</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>35849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>46766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13333</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6189</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3148</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9688</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68304</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>57363</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>76411</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>100610</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>91000</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>111003</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74234</t>
+          <t>71228</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83199</t>
+          <t>77068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>174844</t>
+          <t>139532</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158244</t>
+          <t>126441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192435</t>
+          <t>149204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29349</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21242</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40290</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19552</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9159</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29162</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>48912</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>62003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55391</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48783</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60253</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41519</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45120</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82,64%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58385</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64282</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99904</t>
+          <t>93686</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90906</t>
+          <t>86128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106540</t>
+          <t>99894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13471</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8609</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8723</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5122</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13994</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>29455</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>24050</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>33392</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>64,48%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>89,53%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>23466</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>19021</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>26994</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>75,96%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>46915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>59821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7844</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13249</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>35,52%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7426</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3898</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11871</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>24,04%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>257956</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>241704</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>271275</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>73,24%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>68,63%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>251670</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>236932</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>269341</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>278698</t>
+          <t>219719</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259784</t>
+          <t>205224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>293464</t>
+          <t>231509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>530367</t>
+          <t>477674</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>506638</t>
+          <t>457305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>555525</t>
+          <t>496500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>94246</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>80927</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>110498</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>31,37%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>76616</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>58945</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>91354</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>101208</t>
+          <t>77789</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>65999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120122</t>
+          <t>92284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>177825</t>
+          <t>172035</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>152667</t>
+          <t>153209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>201554</t>
+          <t>192404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>463</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>297508</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>297508</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>297508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
